--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-startup-checklist.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-startup-checklist.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Ask for a 25-50% nonrefundable deposit to hold the date (the pricing calculator suggests 50%), a final payment date, cancellation tiers, a guest minimum, a final guest count date, and service charge versus gratuity. Add a wind, rain and burn ban clause: a tent over the cooking area, induction indoors, or paella cooked at the commissary and delivered hot. State that the client buys the wine for the sangria, and add photo permission. Reuse it for every event.</t>
+          <t>Ask for a 25-50% nonrefundable deposit to hold the date (the pricing calculator suggests 50%), a final payment date, cancellation tiers, a guest minimum, a final guest count date, and service charge versus gratuity. Add a wind, rain and burn ban clause: a canopy over the cooking station, induction with smaller pans indoors (rented, not in the example budget), or paella cooked at the commissary and delivered hot. State that the client buys the wine for the sangria, and add photo permission. Reuse it for every event.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Buy your paella pans and 3-ring burners, and test every ring</t>
+          <t>Open accounts with an approved-source seafood supplier and a cash-and-carry</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Weeks 3-5</t>
+          <t>Weeks 2-4</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Buy pans in three sizes: 36 in (90 cm), 32 in (80 cm) and 26 in (65 cm), plus 3-ring burners with legs. Light each ring, check the regulator and hoses with soapy water, and run a full cook before your first event.</t>
+          <t>Buy only from approved sources, such as a seafood distributor, a broadline distributor or Restaurant Depot. Mussels and clams come with the dealer's shellstock tag: keep it for 90 days. Compare delivery minimums and price lists for seafood, chicken and vegetables.</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Stock hotel pans, sheet pans and utensils</t>
+          <t>Buy your paella pans, 3-ring burners and propane kit, and test every ring</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Standardize on hotel pan sizes so everything stacks, travels and fits the carriers. Label pans and lids by dish.</t>
+          <t>Buy pans in three sizes: 36 in (90 cm), 32 in (80 cm) and 26 in (65 cm), plus 3-ring burners with legs. Light each ring, check the regulator and hoses with soapy water, and run a full cook before your first event. Add eight 20-lb cylinders with regulators and hoses within their date, two extinguishers and a fire blanket, and open an account with a propane refill or exchange service.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Open accounts with an approved-source seafood supplier and a cash-and-carry</t>
+          <t>Stock hotel pans, sheet pans and utensils</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Weeks 2-4</t>
+          <t>Weeks 3-5</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Buy only from approved sources, such as a seafood distributor, a broadline distributor or Restaurant Depot. Mussels and clams come with the dealer's shellstock tag: keep it for 90 days. Compare delivery minimums and price lists for seafood, chicken and vegetables.</t>
+          <t>Standardize on hotel pan sizes so everything stacks, travels and fits the carriers. Label pans and lids by dish.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Buy your live paella station kit: paddles, ladles, wind guards, work table and canopy</t>
+          <t>Set up an importer account for bomba rice, saffron and Spanish pantry items</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Weeks 4-6</t>
+          <t>Weeks 3-5</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>The cooking in front of guests sells the show. Buy long paddles and ladles, wind guards for the burners, a sturdy work table, a cooking canopy, a floor mat and a fire extinguisher you can reach in seconds.</t>
+          <t>Ask for bomba rice, saffron (sold by the gram), smoked paprika, olive oil and stock base from a Spanish food importer. Compare price per quarter, keep a reserve stock for peak season and store rice and saffron dry and sealed.</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Set up an importer account for bomba rice, saffron and Spanish pantry items</t>
+          <t>Buy your live paella station kit: paddles, ladles, wind guards, work table and canopy</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Weeks 3-5</t>
+          <t>Weeks 4-6</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Ask for bomba rice, saffron (sold by the gram), smoked paprika, olive oil and stock base from a Spanish food importer. Compare price per quarter, keep a reserve stock for peak season and store rice and saffron dry and sealed.</t>
+          <t>The cooking in front of guests sells the show. Buy long paddles and ladles, wind guards for the burners, a sturdy work table, a cooking canopy, a floor mat and a fire extinguisher you can reach in seconds.</t>
         </is>
       </c>
     </row>
@@ -2035,22 +2035,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Get food handler cards for your whole team</t>
+          <t>Set your service charge and gratuity policy</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Event staff</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Before the first shift</t>
+          <t>Weeks 3-5</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Many states and counties require a food handler card for anyone handling food. Cards are cheap, online and valid for about 2-3 years.</t>
+          <t>A mandatory service charge is not a tip: the part paid out to staff is wages (IRS Rev. Rul. 2012-18). A gratuity is voluntary and goes to staff. Keep them on separate invoice lines and check your state's sales tax rule.</t>
         </is>
       </c>
     </row>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Train your crew on propane and fire safety: leak checks, extinguishers and shutdown</t>
+          <t>Get food handler cards for your whole team</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Owner / Paella chef</t>
+          <t>Event staff</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Weeks 4-6</t>
+          <t>Before the first shift</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Teach everyone to check connections with soapy water, where the extinguishers and the fire blanket are, and how to close the cylinder valves. Name who watches the burners at all times during service.</t>
+          <t>Many states and counties require a food handler card for anyone handling food. Cards are cheap, online and valid for about 2-3 years.</t>
         </is>
       </c>
     </row>
@@ -2089,76 +2089,76 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
+          <t>Train your crew on propane and fire safety: leak checks, extinguishers and shutdown</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Owner / Paella chef</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Weeks 4-6</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Teach everyone to check connections with soapy water, where the extinguishers and the fire blanket are, and how to close the cylinder valves. Name who watches the burners at all times during service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="74.75" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
           <t>Cover OSHA basics: burns, heat, lifting full pans and cylinders, and driving the van</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Owner / Paella chef</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Weeks 4-6</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Train staff on hot pans, heat exposure, lifting full paella pans and cylinders with two people, and safe van driving. Keep an injury log and a first-aid kit in the van and at every event.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="119.75" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+    <row r="14" ht="119.75" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Train service protocol: the socarrat reveal, uniform, briefing and the nine major allergens</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Paella chef / Event captain</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Weeks 5-7</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Run a pre-event briefing every time. The nine major US allergens include fish and crustacean shellfish (crab, lobster, shrimp); label mussels and clams too. Watch for egg in the aioli, wheat in the bread and noodle paella, sulfites in frozen shrimp, and cross-contact from shared paddles and pans. Send allergy questions to the paella chef.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="74.75" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Set your service charge and gratuity policy</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Owner / Accountant</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Weeks 3-5</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>A mandatory service charge is not a tip: the part paid out to staff is wages (IRS Rev. Rul. 2012-18). A gratuity is voluntary and goes to staff. Keep them on separate invoice lines and check your state's sales tax rule.</t>
         </is>
       </c>
     </row>
@@ -2415,22 +2415,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Prospect corporate clients: office managers, HR and event planners</t>
+          <t>Define your tasting policy for prospects</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Paella chef</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Weeks 5-10</t>
+          <t>Weeks 4-6</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Build a list of nearby offices and drop off sample lunches. Repeat weekday orders make your base, so follow up every contact.</t>
+          <t>Decide who gets a tasting, how many guests attend and whether the fee is credited toward the booking. Track the bookings each tasting produces.</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Make agreements with venues and wedding planners (preferred vendor lists)</t>
+          <t>Create a proposal template with the kit calculator and track leads in your CRM</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Weeks 6-12</t>
+          <t>Weeks 4-6</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Ask each venue how to join its preferred list. Offer a tasting for the planner; their referrals turn into weekend bookings.</t>
+          <t>Build your quote in the pricing calculator: pans by size, rice per guest and the shopping list; the template turns it into a polished quote. Log every inquiry and follow up within 48 hours. Pick catering software that sends the quote, collects the e-signature and takes the deposit by card or ACH.</t>
         </is>
       </c>
     </row>
@@ -2469,22 +2469,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Define your tasting policy for prospects</t>
+          <t>Prospect corporate clients: office managers, HR and event planners</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Owner / Paella chef</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Weeks 4-6</t>
+          <t>Weeks 5-10</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Decide who gets a tasting, how many guests attend and whether the fee is credited toward the booking. Track the bookings each tasting produces.</t>
+          <t>Build a list of nearby offices and drop off sample lunches. Repeat weekday orders make your base, so follow up every contact.</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Create a proposal template with the kit calculator and track leads in your CRM</t>
+          <t>Make agreements with venues and wedding planners (preferred vendor lists)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Weeks 4-6</t>
+          <t>Weeks 6-12</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Build your quote in the pricing calculator: pans by size, rice per guest and the shopping list; the template turns it into a polished quote. Log every inquiry and follow up within 48 hours. Pick catering software that sends the quote, collects the e-signature and takes the deposit by card or ACH.</t>
+          <t>Ask each venue how to join its preferred list. Offer a tasting for the planner; their referrals turn into weekend bookings.</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Event captain</t>
+          <t>Paella chef / Event captain</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
